--- a/EXTRA/testcases_(server_network_&_client_GUI).xlsx
+++ b/EXTRA/testcases_(server_network_&_client_GUI).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20363"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laptop\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560899A2-83BD-42C4-930B-D83B9BF50730}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2D58C6-A57A-427A-A650-BA5EB8D49D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="10" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,16 @@
     <sheet name="TC_08" sheetId="10" r:id="rId9"/>
     <sheet name="TC_09" sheetId="11" r:id="rId10"/>
     <sheet name="TC_10" sheetId="14" r:id="rId11"/>
+    <sheet name="TC_11" sheetId="15" r:id="rId12"/>
+    <sheet name="TC_12" sheetId="16" r:id="rId13"/>
+    <sheet name="TC_13" sheetId="17" r:id="rId14"/>
+    <sheet name="TC_14" sheetId="18" r:id="rId15"/>
+    <sheet name="TC_15" sheetId="19" r:id="rId16"/>
+    <sheet name="TC_16" sheetId="20" r:id="rId17"/>
+    <sheet name="TC_17" sheetId="21" r:id="rId18"/>
+    <sheet name="TC_18" sheetId="22" r:id="rId19"/>
+    <sheet name="TC_19" sheetId="23" r:id="rId20"/>
+    <sheet name="TC_20" sheetId="24" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -400,7 +410,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -408,20 +418,20 @@
       <b/>
       <sz val="11"/>
       <color theme="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -458,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -469,10 +479,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,6 +597,749 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{418D981F-E942-4FE9-B9D6-686457E49477}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2813050" cy="2508250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB85179E-6394-491B-BD2F-41C910E34687}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="2489200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>60064</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81D843D1-A053-49D5-A0A7-993829830697}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7315200" cy="5216264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>110196</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2009C5A-D54C-4F20-B90D-1189BDEA95AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2305050" cy="2421596"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>64450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16370143-5174-40FA-B6E4-F3D258C9684C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7353300" cy="5220650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>538945</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF58FDEA-33B9-4763-92F8-07D863AE47B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6482545" cy="4597400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>27332</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19469023-E592-4E79-9C3E-3D176A654208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6578600" y="19050"/>
+          <a:ext cx="6540500" cy="4631082"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>425449</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>69393</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A6BBB68-53A6-497A-B3A8-0A6373BA875E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10331449" cy="6114593"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>69183</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{882F58FD-915C-4E28-9A9B-E82E694B60A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10566400" y="0"/>
+          <a:ext cx="8654383" cy="6140450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3378EDAB-AC82-4308-B60C-DB56B3A3E9E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9734550" cy="6927850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>518901</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D4AFD9E-653A-4AD1-968E-040897D7B20D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9906000" y="0"/>
+          <a:ext cx="9764501" cy="6838950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>442677</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>169242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B051547E-4383-4D2C-A547-5C04845E2FEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9688277" cy="6925642"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -630,6 +1382,194 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B190BBC-AD3E-43FB-A639-4C943A8C68C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8763000" cy="2438400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72354F35-FE3F-4429-96FA-3FAF9CF07DD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2489200"/>
+          <a:ext cx="8724900" cy="2451100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB14236-FE92-402C-A3B9-55AC81047DD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4978400"/>
+          <a:ext cx="18535650" cy="9556750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1278,19 +2218,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66827C11-D09D-46C6-9119-59F163C93F9A}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" customWidth="1"/>
-    <col min="4" max="4" width="92.85546875" customWidth="1"/>
-    <col min="5" max="5" width="101.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.58203125" customWidth="1"/>
+    <col min="3" max="3" width="72.75" customWidth="1"/>
+    <col min="4" max="4" width="92.83203125" customWidth="1"/>
+    <col min="5" max="5" width="101.58203125" customWidth="1"/>
     <col min="6" max="6" width="51" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.4140625" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1313,7 +2253,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1332,11 +2272,11 @@
       <c r="F2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1355,11 +2295,11 @@
       <c r="F3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1378,11 +2318,11 @@
       <c r="F4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -1401,11 +2341,11 @@
       <c r="F5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1424,11 +2364,11 @@
       <c r="F6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1447,11 +2387,11 @@
       <c r="F7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1470,11 +2410,11 @@
       <c r="F8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -1493,11 +2433,11 @@
       <c r="F9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1516,11 +2456,11 @@
       <c r="F10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -1539,11 +2479,11 @@
       <c r="F11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -1562,11 +2502,11 @@
       <c r="F12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>71</v>
       </c>
@@ -1585,11 +2525,11 @@
       <c r="F13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
@@ -1608,11 +2548,11 @@
       <c r="F14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
@@ -1631,11 +2571,11 @@
       <c r="F15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
@@ -1654,11 +2594,11 @@
       <c r="F16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>92</v>
       </c>
@@ -1677,11 +2617,11 @@
       <c r="F17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>97</v>
       </c>
@@ -1700,11 +2640,11 @@
       <c r="F18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>103</v>
       </c>
@@ -1723,11 +2663,11 @@
       <c r="F19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>108</v>
       </c>
@@ -1746,11 +2686,11 @@
       <c r="F20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>113</v>
       </c>
@@ -1769,7 +2709,7 @@
       <c r="F21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1782,7 +2722,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323F8F8-153A-4CB0-AF1C-6CE9A198EC48}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1792,87 +2732,187 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E855E4-5C77-4344-B7BE-EC0DE64399F9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81725A10-2661-4B3E-A40F-77BEB97EB1DF}">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB9057D-5765-415F-98F8-5127B8491675}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F67D812-2DC0-4302-BEDA-F8A04CC448D8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC684D4-0CA3-4EE2-A1F9-264F33CEE3AE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DEC356-0B74-455E-915F-2249D8E804C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA1A9B-243C-4B36-A5F0-2E9F1426A708}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268EB9B6-C2EE-44AA-9EAE-2E6D8AEB7D23}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95591073-A260-45BC-972A-60E5E13D7899}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2CCAE-E1A7-45A0-9D26-69914FA4BD34}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81725A10-2661-4B3E-A40F-77BEB97EB1DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5CEBB7-AF00-4A0E-A0E2-489E891B91A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8B10E-1E37-421B-9E88-4FC4D39E705F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD214EF-3C39-404C-8D78-F9D2A4CD75BE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/EXTRA/testcases_(server_network_&_client_GUI).xlsx
+++ b/EXTRA/testcases_(server_network_&_client_GUI).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20363"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lap_Trinh_Mang(chau)\prj_final\Project_Laptrinhmang\EXTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2D58C6-A57A-427A-A650-BA5EB8D49D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9E4C38-B633-463A-9272-C8978E963323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="10" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="22620" windowHeight="13500" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,19 +21,23 @@
     <sheet name="TC_05" sheetId="7" r:id="rId6"/>
     <sheet name="TC_06" sheetId="8" r:id="rId7"/>
     <sheet name="TC_07" sheetId="9" r:id="rId8"/>
-    <sheet name="TC_08" sheetId="10" r:id="rId9"/>
-    <sheet name="TC_09" sheetId="11" r:id="rId10"/>
-    <sheet name="TC_10" sheetId="14" r:id="rId11"/>
-    <sheet name="TC_11" sheetId="15" r:id="rId12"/>
-    <sheet name="TC_12" sheetId="16" r:id="rId13"/>
-    <sheet name="TC_13" sheetId="17" r:id="rId14"/>
-    <sheet name="TC_14" sheetId="18" r:id="rId15"/>
-    <sheet name="TC_15" sheetId="19" r:id="rId16"/>
-    <sheet name="TC_16" sheetId="20" r:id="rId17"/>
-    <sheet name="TC_17" sheetId="21" r:id="rId18"/>
-    <sheet name="TC_18" sheetId="22" r:id="rId19"/>
-    <sheet name="TC_19" sheetId="23" r:id="rId20"/>
-    <sheet name="TC_20" sheetId="24" r:id="rId21"/>
+    <sheet name="TC_07#1" sheetId="25" r:id="rId9"/>
+    <sheet name="TC_08" sheetId="10" r:id="rId10"/>
+    <sheet name="TC_08#1" sheetId="27" r:id="rId11"/>
+    <sheet name="TC_09" sheetId="11" r:id="rId12"/>
+    <sheet name="TC_09#1" sheetId="29" r:id="rId13"/>
+    <sheet name="TC_10" sheetId="14" r:id="rId14"/>
+    <sheet name="TC_10#1" sheetId="28" r:id="rId15"/>
+    <sheet name="TC_11" sheetId="15" r:id="rId16"/>
+    <sheet name="TC_12" sheetId="16" r:id="rId17"/>
+    <sheet name="TC_13" sheetId="17" r:id="rId18"/>
+    <sheet name="TC_14" sheetId="18" r:id="rId19"/>
+    <sheet name="TC_15" sheetId="19" r:id="rId20"/>
+    <sheet name="TC_16" sheetId="20" r:id="rId21"/>
+    <sheet name="TC_17" sheetId="21" r:id="rId22"/>
+    <sheet name="TC_18" sheetId="22" r:id="rId23"/>
+    <sheet name="TC_19" sheetId="23" r:id="rId24"/>
+    <sheet name="TC_20" sheetId="24" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="122">
   <si>
     <t>Test Name</t>
   </si>
@@ -180,9 +184,6 @@
   </si>
   <si>
     <t>Clients connect/disconnect liên tục</t>
-  </si>
-  <si>
-    <t>Danh sách online trên ServerForm và tất cả Client được cập nhật đúng, kịp thời và nhất quán giữa các client.</t>
   </si>
   <si>
     <t>Real-time Active Clients List Update</t>
@@ -400,6 +401,21 @@
   </si>
   <si>
     <t>MessageBox hiển thị đúng nội dung lỗi, giao diện không bị crash.</t>
+  </si>
+  <si>
+    <t>Test result #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danh sách online trên ServerForm và tất cả Client được cập nhật đúng, kịp thời </t>
+  </si>
+  <si>
+    <t>Pass(nhưng real-time nên cố định không thay đổi khi có client mới conn)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -410,7 +426,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -418,25 +434,25 @@
       <b/>
       <sz val="11"/>
       <color theme="9"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -455,6 +471,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -468,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -482,6 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,6 +581,153 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>182787</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>115273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFF69B4-28F5-4A8D-B6D2-F25CD132807E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12984387" cy="6973273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>68386</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>77088</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D473EB2-B15D-4624-8255-BDFB8C0224E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12260386" cy="6363588"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>211366</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>115273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{472A0D8D-19FC-4AFB-8C05-532DB042536B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="13012966" cy="6973273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>458795</xdr:colOff>
       <xdr:row>33</xdr:row>
@@ -597,7 +767,56 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>458795</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>115193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF665777-8445-4959-B209-017E8ECA122D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11431595" cy="6401693"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -663,7 +882,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -729,7 +948,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -795,7 +1014,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -861,7 +1080,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -927,7 +1146,56 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>449269</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>105667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1864FB-682D-40AD-9E53-0F44BCF0F49A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11422069" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1054,7 +1322,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1164,7 +1432,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1291,7 +1559,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1340,56 +1608,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>449269</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>105667</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1864FB-682D-40AD-9E53-0F44BCF0F49A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="11422069" cy="6392167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1832,6 +2051,55 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>392111</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>58062</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{841AC327-1729-42CF-B2E0-43E7C68912F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11364911" cy="6535062"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>211366</xdr:colOff>
       <xdr:row>32</xdr:row>
@@ -1860,55 +2128,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="13012966" cy="6258798"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>68386</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>77088</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D473EB2-B15D-4624-8255-BDFB8C0224E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="12260386" cy="6363588"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2217,20 +2436,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66827C11-D09D-46C6-9119-59F163C93F9A}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.58203125" customWidth="1"/>
-    <col min="3" max="3" width="72.75" customWidth="1"/>
-    <col min="4" max="4" width="92.83203125" customWidth="1"/>
-    <col min="5" max="5" width="101.58203125" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="72.7109375" customWidth="1"/>
+    <col min="4" max="4" width="92.85546875" customWidth="1"/>
+    <col min="5" max="5" width="83.5703125" customWidth="1"/>
     <col min="6" max="6" width="51" customWidth="1"/>
-    <col min="7" max="7" width="19.4140625" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2250,10 +2469,13 @@
         <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,19 +2486,22 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" t="s">
-        <v>49</v>
+        <v>57</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2293,36 +2518,42 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>51</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -2339,13 +2570,16 @@
         <v>17</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -2362,13 +2596,16 @@
         <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -2385,13 +2622,16 @@
         <v>27</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -2408,36 +2648,42 @@
         <v>32</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" t="s">
         <v>56</v>
       </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" t="s">
-        <v>49</v>
+        <v>60</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -2451,266 +2697,294 @@
         <v>42</v>
       </c>
       <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
         <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G11" t="s">
-        <v>49</v>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="5" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="G12" t="s">
-        <v>70</v>
-      </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" t="s">
-        <v>70</v>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" t="s">
-        <v>70</v>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" t="s">
-        <v>70</v>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="5" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G16" t="s">
-        <v>70</v>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" t="s">
-        <v>70</v>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="5" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G18" t="s">
-        <v>70</v>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" t="s">
-        <v>70</v>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="B21" t="s">
         <v>113</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>114</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>115</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>116</v>
       </c>
-      <c r="E21" t="s">
-        <v>117</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" t="s">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2720,9 +2994,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323F8F8-153A-4CB0-AF1C-6CE9A198EC48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD214EF-3C39-404C-8D78-F9D2A4CD75BE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2730,9 +3004,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E855E4-5C77-4344-B7BE-EC0DE64399F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFC6955-24B3-4D67-9B8B-5A55C644F187}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2740,9 +3014,9 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB9057D-5765-415F-98F8-5127B8491675}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323F8F8-153A-4CB0-AF1C-6CE9A198EC48}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2750,9 +3024,9 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F67D812-2DC0-4302-BEDA-F8A04CC448D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AE0A1C-BC1C-4426-8F39-5D636AA31E1F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2760,9 +3034,9 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC684D4-0CA3-4EE2-A1F9-264F33CEE3AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E855E4-5C77-4344-B7BE-EC0DE64399F9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2770,9 +3044,9 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DEC356-0B74-455E-915F-2249D8E804C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622BE002-7265-4F01-A038-868008632476}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2780,9 +3054,9 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA1A9B-243C-4B36-A5F0-2E9F1426A708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB9057D-5765-415F-98F8-5127B8491675}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2790,9 +3064,9 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268EB9B6-C2EE-44AA-9EAE-2E6D8AEB7D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F67D812-2DC0-4302-BEDA-F8A04CC448D8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2800,9 +3074,9 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95591073-A260-45BC-972A-60E5E13D7899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC684D4-0CA3-4EE2-A1F9-264F33CEE3AE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2810,9 +3084,9 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2CCAE-E1A7-45A0-9D26-69914FA4BD34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DEC356-0B74-455E-915F-2249D8E804C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2822,7 +3096,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81725A10-2661-4B3E-A40F-77BEB97EB1DF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2830,9 +3104,9 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5CEBB7-AF00-4A0E-A0E2-489E891B91A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA1A9B-243C-4B36-A5F0-2E9F1426A708}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2840,79 +3114,119 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8B10E-1E37-421B-9E88-4FC4D39E705F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268EB9B6-C2EE-44AA-9EAE-2E6D8AEB7D23}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95591073-A260-45BC-972A-60E5E13D7899}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2CCAE-E1A7-45A0-9D26-69914FA4BD34}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5CEBB7-AF00-4A0E-A0E2-489E891B91A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8B10E-1E37-421B-9E88-4FC4D39E705F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD214EF-3C39-404C-8D78-F9D2A4CD75BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12A9794-A6F1-45EA-92E1-CB62038ABC1A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/EXTRA/testcases_(server_network_&_client_GUI).xlsx
+++ b/EXTRA/testcases_(server_network_&_client_GUI).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lap_Trinh_Mang(chau)\prj_final\Project_Laptrinhmang\EXTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9E4C38-B633-463A-9272-C8978E963323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CE6DE5-D610-45D1-B8B0-9FC34627EEFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="22620" windowHeight="13500" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
   <si>
     <t>Test Name</t>
   </si>
@@ -409,13 +409,7 @@
     <t xml:space="preserve">Danh sách online trên ServerForm và tất cả Client được cập nhật đúng, kịp thời </t>
   </si>
   <si>
-    <t>Pass(nhưng real-time nên cố định không thay đổi khi có client mới conn)</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -778,16 +772,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>458795</xdr:colOff>
+      <xdr:colOff>517406</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>115193</xdr:rowOff>
+      <xdr:rowOff>123024</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF665777-8445-4959-B209-017E8ECA122D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DF00AE7-764C-4D9A-BFEA-654EE59BF258}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -804,7 +798,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="11431595" cy="6401693"/>
+          <a:ext cx="11409524" cy="6409524"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2495,7 +2489,7 @@
         <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" t="s">
         <v>48</v>
@@ -2521,7 +2515,7 @@
         <v>58</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" t="s">
         <v>48</v>
@@ -2547,7 +2541,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H4" t="s">
         <v>48</v>
@@ -2573,7 +2567,7 @@
         <v>58</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H5" t="s">
         <v>48</v>
@@ -2599,7 +2593,7 @@
         <v>58</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H6" t="s">
         <v>48</v>
@@ -2625,7 +2619,7 @@
         <v>58</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H7" t="s">
         <v>48</v>
@@ -2729,7 +2723,7 @@
         <v>62</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
         <v>48</v>
@@ -2778,7 +2772,7 @@
         <v>58</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
@@ -2804,7 +2798,7 @@
         <v>58</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H14" t="s">
         <v>69</v>
@@ -2830,7 +2824,7 @@
         <v>58</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H15" t="s">
         <v>69</v>
@@ -2879,7 +2873,7 @@
         <v>58</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>69</v>
@@ -2929,7 +2923,7 @@
         <v>58</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H19" t="s">
         <v>69</v>
@@ -2955,7 +2949,7 @@
         <v>58</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H20" t="s">
         <v>69</v>
@@ -2981,7 +2975,7 @@
         <v>58</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H21" t="s">
         <v>69</v>

--- a/EXTRA/testcases_(server_network_&_client_GUI).xlsx
+++ b/EXTRA/testcases_(server_network_&_client_GUI).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20363"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lap_Trinh_Mang(chau)\prj_final\Project_Laptrinhmang\EXTRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CE6DE5-D610-45D1-B8B0-9FC34627EEFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6748BF8-A72B-4753-B75D-1D10934BDD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="22620" windowHeight="13500" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{C0B55F7B-A299-413E-A73F-B04FCAC81B09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,18 @@
     <sheet name="TC_10" sheetId="14" r:id="rId14"/>
     <sheet name="TC_10#1" sheetId="28" r:id="rId15"/>
     <sheet name="TC_11" sheetId="15" r:id="rId16"/>
-    <sheet name="TC_12" sheetId="16" r:id="rId17"/>
-    <sheet name="TC_13" sheetId="17" r:id="rId18"/>
-    <sheet name="TC_14" sheetId="18" r:id="rId19"/>
-    <sheet name="TC_15" sheetId="19" r:id="rId20"/>
-    <sheet name="TC_16" sheetId="20" r:id="rId21"/>
-    <sheet name="TC_17" sheetId="21" r:id="rId22"/>
-    <sheet name="TC_18" sheetId="22" r:id="rId23"/>
-    <sheet name="TC_19" sheetId="23" r:id="rId24"/>
-    <sheet name="TC_20" sheetId="24" r:id="rId25"/>
+    <sheet name="TC_11#1" sheetId="30" r:id="rId17"/>
+    <sheet name="TC_12" sheetId="16" r:id="rId18"/>
+    <sheet name="TC_13" sheetId="17" r:id="rId19"/>
+    <sheet name="TC_14" sheetId="18" r:id="rId20"/>
+    <sheet name="TC_15" sheetId="19" r:id="rId21"/>
+    <sheet name="TC_15#1" sheetId="31" r:id="rId22"/>
+    <sheet name="TC_16" sheetId="20" r:id="rId23"/>
+    <sheet name="TC_17" sheetId="21" r:id="rId24"/>
+    <sheet name="TC_17#1" sheetId="32" r:id="rId25"/>
+    <sheet name="TC_18" sheetId="22" r:id="rId26"/>
+    <sheet name="TC_19" sheetId="23" r:id="rId27"/>
+    <sheet name="TC_20" sheetId="24" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="121">
   <si>
     <t>Test Name</t>
   </si>
@@ -355,9 +358,6 @@
     <t>Các điều khiển hiển thị đúng, không bị chồng lấp hoặc mất nội dung.</t>
   </si>
   <si>
-    <t>Fail (phóng to: đoạn chat ban đầu bị lệch sang trái; thu nhỏ: mất luôn dòng chat phía tay phải)</t>
-  </si>
-  <si>
     <t>TC_18</t>
   </si>
   <si>
@@ -410,6 +410,13 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Fail (phóng to: đoạn chat ban đầu bị lệch sang trái; 
+thu nhỏ: mất luôn dòng chat phía tay phải)</t>
+  </si>
+  <si>
+    <t>Fail (vẫn còn lỗi cũ và bị lệch phần hiển thị người tham gia)</t>
   </si>
 </sst>
 </file>
@@ -420,7 +427,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -428,25 +435,25 @@
       <b/>
       <sz val="11"/>
       <color theme="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,12 +472,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -484,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -498,7 +499,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -886,6 +892,55 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>89373</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>105460</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE817CF-6700-231C-D79D-2BFCCD1F5D13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3391373" cy="4906060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>355600</xdr:colOff>
       <xdr:row>14</xdr:row>
@@ -942,7 +997,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1008,7 +1063,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1074,7 +1129,56 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>449269</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>105667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1864FB-682D-40AD-9E53-0F44BCF0F49A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11422069" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1140,7 +1244,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1150,17 +1254,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>449269</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>105667</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>433151</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>140663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1864FB-682D-40AD-9E53-0F44BCF0F49A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4233FDB-8C8B-B16B-4758-5774BB30027C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1177,7 +1281,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="11422069" cy="6392167"/>
+          <a:ext cx="9678751" cy="6897063"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1189,7 +1293,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1316,7 +1420,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1426,7 +1530,144 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>68689</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0558153B-5F7B-257D-A3B7-16C55DAE5638}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="0"/>
+          <a:ext cx="10591799" cy="6291689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>114201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6483C72-1A4F-1DC4-9D06-13B112456046}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10623551" y="6350"/>
+          <a:ext cx="7683500" cy="5441851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28898</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BBEFF60-A136-6278-851E-AFF4B703E1C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18319750" y="38100"/>
+          <a:ext cx="7785100" cy="5502598"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1553,7 +1794,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1602,7 +1843,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2431,19 +2672,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66827C11-D09D-46C6-9119-59F163C93F9A}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" customWidth="1"/>
-    <col min="4" max="4" width="92.85546875" customWidth="1"/>
-    <col min="5" max="5" width="83.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.58203125" customWidth="1"/>
+    <col min="3" max="3" width="72.75" customWidth="1"/>
+    <col min="4" max="4" width="92.83203125" customWidth="1"/>
+    <col min="5" max="5" width="83.58203125" customWidth="1"/>
     <col min="6" max="6" width="51" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2463,13 +2704,13 @@
         <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2489,13 +2730,13 @@
         <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2515,13 +2756,13 @@
         <v>58</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2541,13 +2782,13 @@
         <v>58</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -2567,13 +2808,13 @@
         <v>58</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -2593,13 +2834,13 @@
         <v>58</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -2619,13 +2860,13 @@
         <v>58</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -2651,7 +2892,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -2677,7 +2918,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -2703,7 +2944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
@@ -2717,7 +2958,7 @@
         <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>62</v>
@@ -2729,7 +2970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
@@ -2748,11 +2989,14 @@
       <c r="F12" s="5" t="s">
         <v>68</v>
       </c>
+      <c r="G12" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="H12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -2772,13 +3016,13 @@
         <v>58</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>75</v>
       </c>
@@ -2798,13 +3042,13 @@
         <v>58</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -2824,13 +3068,13 @@
         <v>58</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>85</v>
       </c>
@@ -2849,11 +3093,14 @@
       <c r="F16" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="G16" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="H16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>91</v>
       </c>
@@ -2873,13 +3120,13 @@
         <v>58</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="42" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>96</v>
       </c>
@@ -2889,93 +3136,95 @@
       <c r="C18" t="s">
         <v>98</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
         <v>102</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>103</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" t="s">
         <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>106</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" t="s">
         <v>107</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>108</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>109</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>110</v>
-      </c>
-      <c r="E20" t="s">
-        <v>111</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" t="s">
         <v>112</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>113</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>114</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>115</v>
-      </c>
-      <c r="E21" t="s">
-        <v>116</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
         <v>69</v>
@@ -2990,7 +3239,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD214EF-3C39-404C-8D78-F9D2A4CD75BE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3000,7 +3249,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDFC6955-24B3-4D67-9B8B-5A55C644F187}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3010,7 +3259,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9323F8F8-153A-4CB0-AF1C-6CE9A198EC48}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3020,7 +3269,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AE0A1C-BC1C-4426-8F39-5D636AA31E1F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3030,7 +3279,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E855E4-5C77-4344-B7BE-EC0DE64399F9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3040,7 +3289,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622BE002-7265-4F01-A038-868008632476}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3050,7 +3299,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB9057D-5765-415F-98F8-5127B8491675}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3058,9 +3307,9 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F67D812-2DC0-4302-BEDA-F8A04CC448D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D574473-2B08-45AF-B88E-EE0160CFB8D3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3068,9 +3317,9 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC684D4-0CA3-4EE2-A1F9-264F33CEE3AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F67D812-2DC0-4302-BEDA-F8A04CC448D8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3078,9 +3327,9 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DEC356-0B74-455E-915F-2249D8E804C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC684D4-0CA3-4EE2-A1F9-264F33CEE3AE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3090,7 +3339,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81725A10-2661-4B3E-A40F-77BEB97EB1DF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3098,9 +3347,9 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA1A9B-243C-4B36-A5F0-2E9F1426A708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DEC356-0B74-455E-915F-2249D8E804C0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3108,9 +3357,9 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268EB9B6-C2EE-44AA-9EAE-2E6D8AEB7D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA1A9B-243C-4B36-A5F0-2E9F1426A708}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3118,9 +3367,9 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95591073-A260-45BC-972A-60E5E13D7899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB24AEE-0A9C-4A7F-917D-D2B22AC3E2A0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3128,9 +3377,9 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2CCAE-E1A7-45A0-9D26-69914FA4BD34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268EB9B6-C2EE-44AA-9EAE-2E6D8AEB7D23}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3138,9 +3387,9 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5CEBB7-AF00-4A0E-A0E2-489E891B91A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95591073-A260-45BC-972A-60E5E13D7899}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3148,79 +3397,109 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8B10E-1E37-421B-9E88-4FC4D39E705F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D01832F-067B-4294-A797-91D0EA735D9C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2CCAE-E1A7-45A0-9D26-69914FA4BD34}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5CEBB7-AF00-4A0E-A0E2-489E891B91A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB8B10E-1E37-421B-9E88-4FC4D39E705F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2AC27D-3144-4038-958C-0137EBE8BA68}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F9808E-992F-4937-A24F-C3983E2583F9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5A76C6-5563-402B-B5F9-29FAD0318C8B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FBEE27-F12C-490A-84AE-3B5A30905007}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12673609-9E67-44EC-9918-6A3F41B69BA9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1BCB93-8521-4BA1-BC58-FCD8A0C674E9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12A9794-A6F1-45EA-92E1-CB62038ABC1A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
